--- a/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-uso-diagnostico.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-uso-diagnostico.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia/ValueSet/vs-uso-diagnostico</t>
+    <t>https://interoperabilidad.minsal.cl/fhir/ig/urgencia-eventos/ValueSet/vs-uso-diagnostico</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T16:36:45-03:00</t>
+    <t>2026-09-24T11:47:41-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-uso-diagnostico.xlsx
+++ b/fhir/ig/cl-urgencia/0.2.0/ValueSet-vs-uso-diagnostico.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T11:47:41-03:00</t>
+    <t>2026-10-08T00:02:21-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Indica si el diagnóstico corresponde a la hipótesis inicial o al diagnóstico de egreso.</t>
+    <t>Uso del diagnóstico en el episodio de urgencia. Solo se informa el diagnóstico de egreso (DD); la hipótesis diagnóstica se expresa con Condition.verificationStatus = provisional, no con un uso.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,12 +100,6 @@
   </si>
   <si>
     <t>Concept</t>
-  </si>
-  <si>
-    <t>AD</t>
-  </si>
-  <si>
-    <t>Admission diagnosis</t>
   </si>
   <si>
     <t>DD</t>
@@ -384,7 +378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -412,23 +406,15 @@
         <v>31</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
